--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45974</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44676</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45804</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45575</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45153</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>44698</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44503</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>45947</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44554</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44664</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44459</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44823</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44529</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44683</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44459</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44609</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44697</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45321</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45147</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45488</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>44481</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45322</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45640</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>45736</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45244</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45684</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45022</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>45540</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45154</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45166</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45750</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45266</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45084</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>45293</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45264</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44760</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>45455</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44630</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>45076</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45029</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44935</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>44984</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>44806</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>45317</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>44946</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44698</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44964</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45306</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44993</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45049</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45618</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45233</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45619</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45631</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45388</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45540</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45926</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45884</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45293</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45063</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45148</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45805</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45887</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45337</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45401</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45215</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45898</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>45902</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45355</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>46050</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45874</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45072</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45636</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45909</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45908</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45908</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45214</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45072</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45348</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>46141</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45918</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45488</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45921</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44748</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45761</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46140</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45362</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44774</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44920</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44920</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44984</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>46142</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45002</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45244</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>45189</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45229</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45244</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44904</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45819</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>45630</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>45630</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45296</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45229</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45229</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44866</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44606</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>45005</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>45560</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45939</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44897</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45640</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45378</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45582</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45674</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44958</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45313</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45640</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45664</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45296</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45188</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44960</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44755</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45325</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45147</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45755</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45618</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45762</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>45981</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45971</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45985</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>45264</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45160</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45982</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45614</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45988</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>46160</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45678</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>46198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45145</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45070</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44593</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45400</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>46000</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>46000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46000</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>46167</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>46002</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46003</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>46167</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>46007</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45678</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45267</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45456</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46169</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46013</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46169</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>45478</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45174</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>46022</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>46022</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>46030</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>46035</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>46035</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>46038</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>46038</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45820</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46044</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44580</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44873</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>46175</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>46048</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45736</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>46047</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46050</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46050</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>46171</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46055</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>46052</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45470</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45268</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45769</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46059</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45127</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>46062</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>46063</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>46064</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44812</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45546</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>45667</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45618</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46073</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>46073</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45522</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>46188</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>45127</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45667</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>45342</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>46091</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45153</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>46190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>46189</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46101</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>46101</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45393</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45560</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>46111</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>46111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>44897</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46111</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>46111</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>46111</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>46111</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45111</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>46244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45261</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45251</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44672</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46129</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44608</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45071</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45532</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45155</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45314</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45488</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44984</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45489</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>46126</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>46131</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45456</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>46134</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45736</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45684</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45938</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>46247</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>46203</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>46247</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45640</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>46209</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45620</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>46209</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45371</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>46209</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>46185</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>46209</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45111</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45231</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>46253</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44588</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45138</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>44523</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45076</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46253</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46254</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46253</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>46253</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45700</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>46217</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46217</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45093</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44861</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45356</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45371</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46267</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45418</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>44704</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>46267</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45489</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45120</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45582</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45777</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>46273</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45777</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45778</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45778</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46272</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46274</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>46274</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45784</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45784</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>46279</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46276</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45720</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45721</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45740</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45408</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45714</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45740</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45792</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45797</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45797</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45696</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45588</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45189</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44866</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>46239</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45800</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45803</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>44694</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45625</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45557</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45824</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45826</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45831</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45831</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45845</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45845</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45632</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45847</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45849</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45755</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45351</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45261</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45484</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45709</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45881</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44697</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45469</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45240</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45749</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45799</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45674</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44676</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45313</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44978</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44672</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45947</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46160</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>46161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>44903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45575</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45153</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44943</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44554</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44664</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44529</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44683</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45251</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45401</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45244</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45736</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45261</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45393</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45296</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45478</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45696</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45231</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45418</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>46022</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>46022</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45111</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>46030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45455</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44873</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45797</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45797</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44866</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45189</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45805</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45488</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44984</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45819</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>46035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45631</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>46038</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>46038</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44964</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45895</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45378</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45456</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45800</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45897</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>46044</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>46047</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45148</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45902</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45902</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>46050</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46052</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>46055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45912</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44960</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45618</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45916</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>46062</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>46059</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>46063</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46064</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45921</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45803</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45002</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45522</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>46073</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45930</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44694</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45166</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45229</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45229</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45819</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45936</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45630</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45630</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45630</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45630</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45342</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45229</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46091</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45625</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45678</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45939</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45233</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45952</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>46111</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>46111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>46111</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>46111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>46111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45618</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45640</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45636</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>46129</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45145</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>46131</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>46134</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45981</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45684</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>46126</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45640</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45640</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45985</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45971</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45664</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45988</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45582</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44748</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44760</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45127</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>45005</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45874</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45926</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>46000</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45488</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>46000</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>46000</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>46000</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46002</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>46003</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45388</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46140</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>46007</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45954</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45938</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>46013</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>44935</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45736</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45072</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45824</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45540</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45355</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45826</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>46050</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45700</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45203</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>46141</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45796</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45348</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45072</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45071</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45769</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45111</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44523</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>44588</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45313</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45831</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44467</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45362</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45296</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45831</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>46160</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45982</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>46198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45845</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45845</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45632</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45847</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>46167</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45849</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>46167</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45371</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46169</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46169</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45755</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45282</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44579</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>46171</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45532</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45261</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44481</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45747</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45614</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>46189</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>46188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45351</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>44487</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45640</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44749</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44755</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45575</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45484</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>45709</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45189</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45596</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45582</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45560</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45478</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45881</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46203</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44593</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45884</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45325</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>46185</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45736</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>46209</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>46209</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46253</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46253</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46253</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45214</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46253</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>46253</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>46253</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45147</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45138</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45762</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45155</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>46217</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>46217</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45750</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45314</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45337</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>45293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45160</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44806</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45215</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45264</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46267</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44704</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45293</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>46267</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45296</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46272</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44866</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>46274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45470</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>46273</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45619</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>46279</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45231</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45175</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>46239</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46286</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45371</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45322</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45400</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46286</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46276</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>44606</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45489</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46190</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45266</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45076</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46244</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>46288</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45546</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45022</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44861</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>46247</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46247</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>44937</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44580</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45231</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45049</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45070</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44958</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45618</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45111</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45268</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44946</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44747</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45488</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45321</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45317</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45456</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45356</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45488</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45540</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45761</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45120</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45667</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44993</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45063</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>44630</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45620</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45674</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45618</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>44920</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>44920</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45306</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45684</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45264</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45215</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45667</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>44698</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45777</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45614</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45778</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45784</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45784</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45740</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45740</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45408</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45720</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45721</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45714</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45792</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44697</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45469</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45240</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45799</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45674</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>44676</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45313</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44978</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44672</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45947</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46160</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>46161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>44903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45575</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45153</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44943</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44554</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44664</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44529</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44683</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45251</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45401</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45244</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45736</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45261</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45393</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45296</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45478</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45696</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45231</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45418</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>46022</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>46022</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45111</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>46030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45455</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44873</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45797</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45797</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44866</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45189</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45805</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45488</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44984</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45819</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>46035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45631</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>46038</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>46038</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44964</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45895</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45378</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45456</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45800</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45897</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>46044</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>46047</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45148</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45902</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45902</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>46050</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46052</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>46055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45912</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44960</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45618</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45916</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>46062</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>46059</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>46063</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46064</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45921</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45803</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45002</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45522</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>46073</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45930</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44694</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45166</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45229</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45229</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45819</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45936</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45630</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45630</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45630</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45630</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45342</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45229</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46091</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45625</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45678</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45939</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45233</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45952</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>46111</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>46111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>46111</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>46111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>46111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45618</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45640</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45636</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>46129</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45145</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>46131</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>46134</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45981</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45684</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>46126</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45640</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45640</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45985</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45971</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45664</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45988</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45582</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44748</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44760</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45127</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>45005</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45874</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45926</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>46000</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45488</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>46000</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>46000</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>46000</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46002</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>46003</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45388</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46140</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>46007</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45954</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45938</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>46013</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>44935</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45736</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45072</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45824</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45540</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45355</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45826</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>46050</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45700</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45203</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>46141</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45796</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45348</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45072</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45071</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45769</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45111</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44523</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>44588</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45313</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45831</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44467</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45362</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45296</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45831</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>46160</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45982</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>46198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45845</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45845</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45632</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45847</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>46167</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45849</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>46167</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45371</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46169</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46169</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45755</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45282</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44579</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>46171</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45532</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45261</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44481</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45747</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45614</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>46189</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>46188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45351</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>44487</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45640</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44749</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44755</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45575</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45484</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>45709</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45189</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45596</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45582</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45560</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45478</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45881</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46203</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44593</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45884</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45325</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>46185</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45736</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>46209</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>46209</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46253</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46253</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46253</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45214</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46253</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>46253</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>46253</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45147</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45138</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45762</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45155</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>46217</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>46217</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45750</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45314</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45337</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>45293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45160</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44806</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45215</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45264</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46267</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44704</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45293</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>46267</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45296</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46272</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44866</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>46274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45470</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>46273</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45619</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>46279</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45231</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45175</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>46239</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46286</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45371</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45322</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45400</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46286</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46276</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>44606</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45489</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46190</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45266</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45076</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46244</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>46288</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45546</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45022</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44861</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>46247</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46247</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>44937</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44580</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45231</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45049</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45070</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44958</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45618</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45111</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45268</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44946</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44747</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45488</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45321</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45317</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45456</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45356</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45488</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45540</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45761</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45120</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45667</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44993</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45063</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>44630</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45620</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45674</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45618</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>44920</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>44920</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45306</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45684</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45264</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45215</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45667</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>44698</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45777</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45614</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45778</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45784</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45784</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45740</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45740</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45408</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45720</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45721</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45714</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45792</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44697</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45469</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45240</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45749</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45799</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45974</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44676</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45575</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44672</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45947</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45153</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44698</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44503</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44664</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44529</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44683</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45147</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45488</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45596</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44487</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>44481</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45322</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45640</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>46002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44747</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>45231</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46003</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45720</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>45721</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46007</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>45244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45684</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>46013</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45740</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45408</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45022</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45805</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45540</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>46022</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>46022</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45166</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>46030</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45750</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45266</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45902</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45902</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45792</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46038</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46038</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45084</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>45820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45908</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45728</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45293</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45797</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45911</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46044</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45696</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45912</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46047</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44866</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45916</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45800</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46050</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45921</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44694</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44760</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>46052</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44630</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>45455</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45625</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45930</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>46062</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45630</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45229</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45111</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45819</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44672</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46064</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45630</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45630</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45630</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45076</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45819</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45229</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45229</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44896</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45029</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44935</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44984</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45618</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44806</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45939</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45317</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>46078</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44946</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45557</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45952</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45582</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45342</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>46091</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44897</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45306</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44993</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>46101</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45049</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>46101</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44937</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45618</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45233</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45971</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>46111</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>46111</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>46111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45619</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45985</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>46111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45631</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45986</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45988</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45824</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45826</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44672</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45203</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>46129</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45293</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45831</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>46000</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46000</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>46000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>46000</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45063</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45148</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>46126</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>46131</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>46134</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45337</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44715</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45401</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45215</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45954</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45388</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45845</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45540</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45636</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45926</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45632</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45847</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44749</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45849</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45214</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45575</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45488</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45231</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45755</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44748</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45761</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45362</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>44774</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45355</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46050</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44920</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44920</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45874</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44984</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45072</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45002</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45189</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45296</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44866</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45796</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45072</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45348</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45005</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45560</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44897</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>46141</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45640</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45351</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46142</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45378</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45582</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45674</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44958</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45313</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45175</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45640</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45261</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45664</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45296</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44960</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>44755</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45325</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45147</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45755</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45982</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45618</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>46160</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46198</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45762</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>46167</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45484</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45709</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>46169</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45264</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45174</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45614</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46171</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>44812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45145</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45070</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44593</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45400</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>46188</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>46189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45267</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45456</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45478</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>46202</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>46209</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>46209</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>46209</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46185</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46209</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44580</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44873</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45736</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>46217</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>46217</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45470</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45268</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45769</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45127</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>46267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45546</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>46267</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45667</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45618</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>46273</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>46272</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45522</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46274</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46274</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46279</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45127</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45667</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46239</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46286</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46276</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46190</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45393</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45560</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46244</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>46286</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44897</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45111</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45111</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>46175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45251</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44608</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45215</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45071</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45532</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45314</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>46247</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45488</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44984</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>45489</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45456</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45282</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>46247</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>45736</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45684</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46253</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>46295</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45055</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>46294</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45640</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46254</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>46253</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>46253</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>46294</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45620</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>46253</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>46253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>46294</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45111</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45231</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44588</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45138</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44523</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45700</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45296</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45093</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45356</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45371</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45418</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>44704</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45489</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45120</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45582</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45777</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45614</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>45777</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45778</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45784</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45784</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44697</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45469</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45240</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45749</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45799</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45974</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44676</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45674</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45575</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44672</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45947</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45153</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44698</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44503</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44664</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44529</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44683</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45147</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45488</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45596</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44487</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>44481</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45322</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45640</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>46002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44747</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>45231</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46003</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45720</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>45721</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46007</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>45244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45684</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>46013</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45740</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45408</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45022</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45805</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45540</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>46022</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>46022</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45166</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>46030</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45750</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45266</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45902</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45902</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45792</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46038</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46038</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45084</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>45820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45908</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45728</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45293</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45797</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45911</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46044</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45696</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45912</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46047</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44866</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45916</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45800</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46050</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45921</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44694</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44760</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>46052</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44630</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>45455</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45625</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45930</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>46062</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45630</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45229</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45111</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45819</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44672</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46064</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45630</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45630</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45630</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45076</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45819</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45229</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45229</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44896</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45029</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44935</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44984</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45618</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44806</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45939</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45317</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>46078</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44946</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45557</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45952</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45582</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45342</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>46091</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44897</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45306</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44993</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>46101</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45049</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>46101</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44937</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45618</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45233</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45971</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>46111</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>46111</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>46111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45619</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45985</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>46111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45631</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45986</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45988</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45824</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45826</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44672</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45203</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>46129</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45293</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45831</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>46000</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46000</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>46000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>46000</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45063</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45148</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>46126</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>46131</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>46134</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45337</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44715</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45401</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45215</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45954</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45388</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45845</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45540</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45636</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45926</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45632</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45847</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44749</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45849</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45214</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45575</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45488</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45231</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45755</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44748</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45761</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45362</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>44774</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45355</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46050</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44920</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44920</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45874</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44984</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45072</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45002</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45189</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45296</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44866</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45796</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45072</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45348</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45005</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45560</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44897</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>46141</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45640</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45351</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46142</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45378</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45582</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45674</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44958</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45313</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45175</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45640</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45261</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45664</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45296</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44960</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>44755</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45325</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45147</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45755</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45982</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45618</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>46160</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46198</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45762</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>46167</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45484</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45709</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>46169</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45264</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45174</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45614</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46171</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>44812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45145</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45070</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44593</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45400</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>46188</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>46189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45267</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45456</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45478</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>46202</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>46209</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>46209</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>46209</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46185</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46209</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44580</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44873</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45736</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>46217</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>46217</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45470</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45268</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45769</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45127</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>46267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45546</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>46267</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45667</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45618</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>46273</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>46272</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45522</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46274</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46274</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46279</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45127</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45667</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46239</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46286</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46276</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46190</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45393</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45560</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46244</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>46286</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44897</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45111</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45111</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>46175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45251</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44608</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45215</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45071</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45532</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45314</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>46247</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45488</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44984</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>45489</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45456</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45282</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>46247</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>45736</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45684</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46253</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>46295</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45055</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>46294</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45640</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46254</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>46253</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>46253</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>46294</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45620</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>46253</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>46253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>46294</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45111</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45231</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44588</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45138</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44523</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45700</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45296</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45093</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45356</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45371</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45418</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>44704</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45489</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45120</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45582</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45777</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45614</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>45777</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45778</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45784</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45784</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44697</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45469</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45240</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45749</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45799</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>44676</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45974</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45575</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44672</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44698</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45677</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45947</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44503</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45539</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>46161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>45575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44554</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44664</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44630</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44823</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44704</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44834</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44529</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45313</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44697</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44747</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45736</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45321</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45317</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45456</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45356</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45362</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45488</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45261</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>44774</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45296</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45393</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45296</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>45755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45120</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45667</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45478</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45401</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45418</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>45063</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44630</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45805</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45111</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45282</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45819</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45618</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45455</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44873</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>44920</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44920</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45895</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45895</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45897</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45902</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44984</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44984</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45306</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45684</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45631</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44579</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45378</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45456</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45532</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45264</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45215</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45667</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44481</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44698</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45777</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45614</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45778</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45747</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45912</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45777</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44897</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45127</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45784</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45784</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45918</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45618</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45921</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44487</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45522</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45640</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45740</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44755</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45740</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45575</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45408</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45029</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45720</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45792</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45930</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45696</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45189</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45596</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45596</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45560</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45166</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>45797</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45478</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44866</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45189</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>45229</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44896</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45560</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>45229</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45244</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45588</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45630</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45630</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45630</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45630</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44672</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44593</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45678</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45800</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44904</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45819</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45229</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45325</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45803</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45233</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45736</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44694</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45625</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45557</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45939</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45214</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45093</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45147</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45138</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45618</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45826</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44929</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45155</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45640</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45831</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>45636</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45153</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45145</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45684</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45640</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45640</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44608</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45750</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45314</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45582</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45582</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45337</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44748</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45293</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45847</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45849</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44760</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45160</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44806</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45264</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44984</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45755</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44704</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45293</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45296</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45488</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45489</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45261</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44866</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45351</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45678</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45470</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45484</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44897</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45981</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44935</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45709</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45736</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45881</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45055</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45619</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45267</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46101</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45231</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45700</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45175</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>46101</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45203</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45971</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45986</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45071</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>46111</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>46111</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45769</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46111</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45988</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>46111</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>46111</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44523</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46111</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45371</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>44588</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45322</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45400</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44672</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46000</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46000</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45489</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>46129</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>46002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>46131</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45266</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46134</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45084</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>46003</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>46126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45076</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45546</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>46007</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45022</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44861</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>44937</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44580</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>46013</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45231</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>46022</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>46022</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45049</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45874</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45926</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46030</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45070</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45388</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46140</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44958</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46035</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>46035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45820</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46038</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45618</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45111</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45111</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45268</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45072</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>46044</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>46047</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>45540</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45355</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>46050</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44946</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>46142</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>46050</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>46141</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45796</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>46052</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45348</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45072</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46055</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>46062</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>46059</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46063</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46064</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46073</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>46078</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45342</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>46091</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45982</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>46198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>46167</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>46167</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45174</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>46169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>46171</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>44812</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>46189</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>46202</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46203</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46185</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>46209</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>46209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46209</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>46209</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>46217</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46217</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46267</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46272</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46274</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46274</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46273</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>46279</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>46239</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>46286</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>46286</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>46276</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>46190</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>46244</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>46247</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>46247</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>46175</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>46294</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>46294</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>46253</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>46294</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>46254</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>46253</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46253</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>46253</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>46253</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46295</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>46253</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>46297</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46303</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46303</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>46303</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>46302</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44697</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45469</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45240</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45749</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45799</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>44676</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45974</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45575</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44672</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44698</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45677</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45947</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44503</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45539</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>46161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>45575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44554</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44664</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44630</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44823</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44704</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44834</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44529</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45313</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44697</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44747</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45736</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45321</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45317</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45456</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45356</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45362</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45488</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45261</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>44774</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45296</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45393</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45296</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>45755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45120</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45667</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45478</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45401</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45418</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>45063</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44630</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45805</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45111</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45282</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45819</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45618</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45455</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44873</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>44920</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44920</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45895</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45895</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45897</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45902</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44984</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44984</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45306</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45684</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45631</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44579</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45378</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45456</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45532</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45264</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45215</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45667</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44481</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44698</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45777</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45614</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45778</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45747</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45912</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45777</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44897</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45127</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45784</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45784</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45918</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45618</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45921</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44487</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45522</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45640</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45740</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44755</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45740</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45575</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45408</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45029</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45720</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45792</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45930</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45696</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45189</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45596</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45596</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45560</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45166</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>45797</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45478</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44866</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45189</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>45229</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44896</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45560</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>45229</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45244</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45588</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45630</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45630</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45630</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45630</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44672</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44593</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45678</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45800</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44904</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45819</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45229</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45325</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45803</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45233</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45736</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44694</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45625</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45557</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45939</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45214</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45093</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45147</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45138</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45618</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45826</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44929</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45155</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45640</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45831</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>45636</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45153</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45145</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45684</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45640</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45640</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44608</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45750</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45314</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45582</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45582</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45337</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44748</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45293</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45847</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45849</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44760</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45160</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44806</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45264</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44984</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45755</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44704</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45293</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45296</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45488</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45489</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45261</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44866</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45351</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45678</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45470</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45484</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44897</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45981</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44935</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45709</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45736</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45881</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45055</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45619</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45267</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46101</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45231</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45700</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45175</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>46101</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45203</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45971</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45986</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45071</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>46111</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>46111</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45769</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46111</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45988</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>46111</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>46111</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44523</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46111</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45371</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>44588</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45322</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45400</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44672</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46000</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46000</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45489</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>46129</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>46002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>46131</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45266</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46134</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45084</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>46003</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>46126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45076</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45546</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>46007</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45022</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44861</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>44937</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44580</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>46013</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45231</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>46022</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>46022</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45049</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45874</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45926</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46030</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45070</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45388</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46140</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44958</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46035</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>46035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45820</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46038</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45618</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45111</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45111</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45268</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45072</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>46044</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>46047</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>45540</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45355</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>46050</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44946</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>46142</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>46050</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>46141</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45796</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>46052</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45348</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45072</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46055</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>46062</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>46059</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46063</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46064</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46073</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>46078</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45342</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>46091</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45982</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>46198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>46167</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>46167</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45174</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>46169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>46171</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>44812</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>46189</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>46202</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46203</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46185</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>46209</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>46209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46209</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>46209</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>46217</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46217</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46267</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46272</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46274</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46274</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46273</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>46279</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>46239</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>46286</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>46286</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>46276</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>46190</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>46244</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>46247</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>46247</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>46175</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>46294</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>46294</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>46253</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>46294</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>46254</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>46253</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46253</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>46253</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>46253</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46295</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>46253</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>46297</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46303</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46303</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>46303</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>46302</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44697</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45469</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45240</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45749</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45799</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45974</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44676</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45804</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45575</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45153</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>44698</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45947</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44503</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44664</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44529</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44683</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45596</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44487</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45488</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45488</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45147</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45322</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45097</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45640</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45231</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45478</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>45736</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45684</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>45022</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45154</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45540</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45166</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45084</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45293</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44760</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45455</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44630</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>45111</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45076</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44935</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45618</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44806</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45317</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44946</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44698</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>44897</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44964</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45306</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44937</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45619</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45618</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45388</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45540</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45884</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45805</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45887</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45293</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45895</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45148</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45895</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45355</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>46050</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45874</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45337</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45796</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45898</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45072</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>45348</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45902</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45902</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45401</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45911</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45215</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>46142</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45912</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45916</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45921</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45214</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45630</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45229</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45819</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45630</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45630</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45630</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45819</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45229</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45229</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44896</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45575</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45488</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45231</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44748</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>45761</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45939</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45362</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44774</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44920</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44920</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45189</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45296</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44606</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45005</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45560</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45982</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44897</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45640</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45378</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45582</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45674</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>46160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44958</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45313</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>46198</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45640</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45664</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>45296</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45981</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44960</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44755</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45971</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45325</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45985</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45147</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>46167</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45755</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>46169</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45618</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>45762</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45174</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46000</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>46000</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>46000</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>46000</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>46002</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45264</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>46003</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45160</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>46007</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45614</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>46013</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45678</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>46022</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46022</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45145</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45070</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46030</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45400</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46035</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>46171</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>46038</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46038</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45820</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44812</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>46048</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>46047</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45678</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45267</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45456</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>46050</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>46055</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46052</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>46059</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46062</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46063</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45478</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>46064</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>46188</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46073</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46078</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45342</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46189</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>46091</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44580</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44873</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45736</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46101</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>46101</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45470</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45268</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>46111</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>46111</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>46111</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46111</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46111</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45127</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45546</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45667</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45618</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44672</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46129</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46202</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>46126</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46131</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45522</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46134</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>46203</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45127</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45667</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45954</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46209</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45153</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>46209</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45393</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45560</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>46217</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46217</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45111</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45111</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45261</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>46272</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44608</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45215</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45071</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45532</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45155</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45314</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45488</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>46274</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>46274</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45489</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45456</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45736</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45684</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45055</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45640</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>46239</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45620</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46286</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45371</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45111</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45231</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46276</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44588</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45138</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46244</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44523</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45076</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46286</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46288</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45700</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>46247</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46247</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>46295</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44861</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45356</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45371</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46294</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45418</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44704</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>46253</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>46253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>46253</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45489</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45120</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>46294</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>46253</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46253</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>46294</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45582</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>45777</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>45614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45778</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>46297</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45784</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45784</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46303</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>46303</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46303</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45720</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45721</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45408</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>46302</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45714</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45740</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45792</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45797</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45797</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45696</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45588</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44866</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45800</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>46308</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>46308</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45803</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44694</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45625</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45557</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>46311</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46267</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45824</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45826</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45831</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45845</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45845</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45632</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45847</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45849</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45755</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45351</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45261</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45484</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45709</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45881</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44697</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45469</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45240</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45749</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45799</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45974</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44676</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45804</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44491</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45575</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45153</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>44698</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45947</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44503</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>46160</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45352</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44664</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44651</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44581</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>44527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44563</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44704</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44529</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44683</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44609</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44678</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45596</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44487</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45488</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45488</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45147</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45322</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45097</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45640</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45231</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45478</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>45736</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45684</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>45022</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45154</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45540</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45166</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45084</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45293</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44760</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45455</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44630</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>45111</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45076</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44935</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45618</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44806</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45317</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44946</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44698</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>44897</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44964</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45306</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44937</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45619</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45618</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45388</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45540</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45884</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45805</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45887</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45293</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45895</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45148</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45895</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45355</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>46050</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45874</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45337</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45796</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45898</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45072</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>45348</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45902</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45902</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45401</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45911</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45215</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>46142</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45912</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45916</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45921</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45214</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45630</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45229</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45819</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45630</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45630</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45630</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45819</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45229</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45229</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44896</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45575</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45488</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45231</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44748</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>45761</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45939</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45362</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44774</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44920</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44920</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45189</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45296</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44606</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45005</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45560</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45982</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44897</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45640</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45378</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45582</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45674</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>46160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44958</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45313</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>46198</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45640</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45664</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>45296</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45981</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44960</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44755</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45971</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45325</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45985</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45147</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>46167</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45755</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>46169</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45618</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>45762</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45174</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46000</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>46000</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>46000</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>46000</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>46002</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45264</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>46003</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45160</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>46007</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45614</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>46013</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45678</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>46022</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46022</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45145</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45070</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46030</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45400</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46035</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>46171</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>46038</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46038</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45820</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44812</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>46048</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>46047</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45678</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45267</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45456</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>46050</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>46055</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46052</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>46059</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46062</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46063</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45478</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>46064</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>46188</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46073</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46078</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45342</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46189</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>46091</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44580</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44873</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45736</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46101</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>46101</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45470</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45268</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>46111</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>46111</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>46111</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46111</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46111</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45127</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45546</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45667</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45618</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44672</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46129</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46202</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>46126</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46131</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45522</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46134</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>46203</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45127</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45667</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45954</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46209</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45153</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>46209</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45393</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45560</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>46217</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46217</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45111</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45111</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45261</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>46272</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44608</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45215</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45071</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45532</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45155</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45314</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45488</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>46274</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>46274</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45489</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45456</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45736</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45684</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45055</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45640</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>46239</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45620</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46286</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45371</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45111</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45231</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46276</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44588</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45138</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46244</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44523</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45076</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46286</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46288</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45700</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>46247</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46247</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>46295</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44861</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45356</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45371</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46294</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45418</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44704</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>46253</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>46253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>46253</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45489</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45120</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>46294</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>46253</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46253</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>46294</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45582</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>45777</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>45614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45778</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>46297</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45784</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45784</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46303</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>46303</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46303</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45720</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45721</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45408</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>46302</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45714</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45740</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45792</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45797</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45797</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45696</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45588</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44866</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45800</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>46308</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>46308</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45803</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44694</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45625</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45557</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>46311</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46267</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45824</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45826</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45831</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45845</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45845</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45632</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45847</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45849</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45755</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45351</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45261</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45484</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45709</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45881</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44697</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45469</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45240</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45749</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45799</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45974</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45804</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44676</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>44691</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46160</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>46161</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45575</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44672</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44978</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>44698</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44503</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>45539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45153</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45352</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>44889</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44554</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44664</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44509</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>44651</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44581</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44806</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44866</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44630</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>44866</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>44823</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>44704</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44529</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>44609</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44678</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45076</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45887</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45244</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44774</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>44861</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44580</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45898</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>45401</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>45902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45982</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>46198</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45736</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45911</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45912</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45070</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45921</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45618</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>46167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45111</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45268</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>46169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>46169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45930</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45229</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45229</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45819</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45630</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45630</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45630</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44672</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44904</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45819</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45229</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44747</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45939</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45321</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45393</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45317</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45296</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45456</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45478</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45356</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>44812</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45488</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45540</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45952</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45761</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45120</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>45667</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46189</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>46188</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44993</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45063</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44630</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>46202</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45620</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45981</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>46203</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45674</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45618</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44920</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44920</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45971</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>45986</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>46209</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>46209</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>46209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45988</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45418</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45306</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45684</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45231</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>45097</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46217</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46217</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45264</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45215</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>46000</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44698</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>46000</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>46000</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>46000</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45777</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45614</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45778</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45777</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>46003</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45784</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45784</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>46007</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>46279</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>46013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46022</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>46022</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>46239</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46286</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45740</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45408</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45720</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45721</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45714</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45696</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46035</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46035</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45820</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45111</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>46286</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>46190</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45797</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45797</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>46044</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44866</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46048</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46047</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45588</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46244</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45800</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46288</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46050</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>46052</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45803</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46247</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>46247</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44694</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45625</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45557</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46059</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46064</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46294</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46073</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46294</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>46253</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46294</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45824</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45826</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>46078</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46254</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46253</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46253</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>46253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>46253</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>46295</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>46253</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45455</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>44873</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45342</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45831</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>46091</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>46101</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45845</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45845</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>46101</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45632</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45847</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45849</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45488</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>46111</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>46111</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46111</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46111</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45755</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>44984</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44984</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46297</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>46111</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46303</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>46303</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45261</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45631</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46303</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>46302</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45484</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>46129</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46308</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46308</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45709</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>46131</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45881</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45378</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45456</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>46134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45884</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>46126</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>46267</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44960</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45618</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>46267</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45874</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45926</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>46311</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45522</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45388</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>46140</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45954</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45938</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46272</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45029</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>46273</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45072</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45355</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46050</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45166</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46276</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>46142</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46274</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45796</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45348</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45560</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45072</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45678</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45233</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>46160</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45618</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44929</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45640</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45636</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45147</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45145</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45684</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45640</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45640</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44608</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45664</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45582</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45582</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44748</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>44760</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45127</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45005</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44984</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45488</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45489</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45678</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44897</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44935</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45736</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45728</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45055</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45267</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45700</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45203</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45071</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45769</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>45111</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>44523</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>44588</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45313</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45362</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45296</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>45371</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>44579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45532</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>45127</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45614</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45640</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44749</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44755</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45575</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45596</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45596</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45582</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45560</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45478</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45325</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45736</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45214</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45093</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45147</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45138</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45762</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45155</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45153</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45750</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45314</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45337</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>44715</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45293</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44806</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45215</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45264</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44704</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45293</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45296</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44866</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45470</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45619</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>45231</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45175</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45371</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45322</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45400</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>44606</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45489</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45266</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>44697</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>45469</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45240</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45749</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45799</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt MUNKEDAL.xlsx
+++ b/Översikt MUNKEDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45517</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>44581</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45974</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45804</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45674</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44676</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>44691</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46160</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>46161</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45575</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44672</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44978</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>44698</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44503</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>45539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45153</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45352</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>44889</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44554</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44664</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44509</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>44651</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44581</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44806</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44866</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44630</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>44866</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>44823</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>44704</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44529</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>44609</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44678</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45076</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45887</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45244</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44774</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>44861</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44580</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45898</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>45401</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>45902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45982</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>46198</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45736</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45911</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45912</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45070</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45921</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45618</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>46167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45111</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45268</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>46169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>46169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45930</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45229</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45229</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45819</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45630</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45630</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45630</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44672</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44904</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45819</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45229</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44747</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45939</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45321</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45393</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45317</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45296</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45456</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45478</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45356</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>44812</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45488</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45540</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45952</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45761</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45120</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>45667</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46189</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>46188</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44993</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45063</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44630</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>46202</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45620</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45981</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>46203</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45674</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45618</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44920</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44920</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45971</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>45986</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>46209</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>46209</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>46209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45988</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45418</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45306</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45684</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45231</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>45097</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46217</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46217</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45264</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45215</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>46000</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44698</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>46000</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>46000</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>46000</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45777</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45614</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45778</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45777</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>46003</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45784</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45784</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>46007</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>46279</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>46013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46022</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>46022</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>46239</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46286</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45740</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45408</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45720</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45721</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45714</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45696</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46035</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46035</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45820</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45111</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>46286</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>46190</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45797</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45797</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>46044</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44866</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46048</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46047</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45588</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46244</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45800</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46288</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46050</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>46052</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45803</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46247</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>46247</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44694</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45625</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45557</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46059</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46064</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46294</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46073</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46294</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>46253</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46294</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45824</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45826</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>46078</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46254</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46253</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46253</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>46253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>46253</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>46295</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>46253</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45455</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>44873</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45342</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45831</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>46091</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>46101</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45845</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45845</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>46101</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45632</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45847</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45849</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45488</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>46111</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>46111</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46111</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46111</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45755</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>44984</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44984</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46297</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>46111</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46303</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>46303</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45261</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45631</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46303</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>46302</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45484</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>46129</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46308</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46308</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45709</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>46131</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45881</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45378</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45456</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>46134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45884</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>46126</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>46267</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44960</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45618</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>46267</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45874</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45926</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>46311</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45522</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45388</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>46140</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45954</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45938</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46272</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45029</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>46273</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45072</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45355</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46050</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45166</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46276</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>46142</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46274</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45796</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45348</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45560</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45072</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45678</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45233</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>46160</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45618</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44929</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45640</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45636</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45147</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45145</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45684</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45640</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45640</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44608</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45664</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45582</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45582</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44748</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>44760</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45127</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45005</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44984</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45488</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45489</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45678</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44897</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44935</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45736</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45728</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45055</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45267</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45700</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45203</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45071</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45769</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>45111</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>44523</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>44588</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45313</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45362</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45296</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>45371</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>44579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45532</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>45127</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45614</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45640</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44749</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44755</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45575</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45596</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45596</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45582</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45560</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45478</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45325</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45736</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45214</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45093</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45147</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45138</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45762</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45155</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45153</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45750</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45314</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45337</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>44715</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45293</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44806</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45215</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45264</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44704</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45293</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45296</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44866</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45470</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45619</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>45231</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45175</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45371</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45322</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45400</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>44606</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45489</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45266</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>44697</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>45469</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45240</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45749</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45799</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
